--- a/resultados/umuarama/erros_varredura.xlsx
+++ b/resultados/umuarama/erros_varredura.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.umuarama.pr.gov.br/secretaria/meio-ambiente</t>
+          <t>https://www.umuarama.pr.gov.br/download_mp3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-04 01:57:51</t>
+          <t>2026-08-04 20:43:05</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.umuarama.pr.gov.br/public/download_mp3</t>
+          <t>https://www.umuarama.pr.gov.br/secretaria/meio-ambiente</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -496,11 +496,11 @@
         <v>500</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-04 02:01:00</t>
+          <t>2026-08-04 20:46:02</t>
         </is>
       </c>
     </row>
@@ -512,23 +512,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://zonaazuldigital.umuarama.pr.gov.br/2025/10/20/home/</t>
+          <t>https://www.umuarama.pr.gov.br/public/download_mp3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-04 02:04:55</t>
+          <t>2026-08-04 20:50:20</t>
         </is>
       </c>
     </row>
@@ -540,23 +540,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://umuarama.pr.gov.br/secretaria/meio-ambiente</t>
+          <t>https://zonaazuldigital.umuarama.pr.gov.br/2025/10/20/home/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-04 02:12:29</t>
+          <t>2026-08-04 20:54:41</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://umuarama.pr.gov.br/public/download_mp3</t>
+          <t>https://umuarama.pr.gov.br/download_mp3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -580,11 +580,11 @@
         <v>500</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-04 02:12:54</t>
+          <t>2026-08-04 20:55:58</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>http://www.umuarama.pr.gov.br/secretarias/educacao</t>
+          <t>https://umuarama.pr.gov.br/secretaria/meio-ambiente</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-04 02:16:29</t>
+          <t>2026-08-04 21:08:02</t>
         </is>
       </c>
     </row>
@@ -624,23 +624,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>http://www.umuarama.pr.gov.br/secretarias/educacao</t>
+          <t>https://umuarama.pr.gov.br/public/download_mp3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-04 02:16:47</t>
+          <t>2026-08-04 21:08:21</t>
         </is>
       </c>
     </row>
@@ -652,23 +652,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.umuarama.pr.gov.br/noticias/assistencia-social/www.flickr.com/photos/167581318@N03/albums/72177720334168307/</t>
+          <t>http://www.obituario.umuarama.pr.gov.br/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04 02:21:17</t>
+          <t>2026-08-04 21:11:52</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.umuarama.pr.gov.br/noticias/assistencia-social/www.flickr.com/photos/167581318@N03/albums/72177720334168307/</t>
+          <t>http://www.umuarama.pr.gov.br/secretarias/educacao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -692,11 +692,11 @@
         <v>404</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-04 02:21:39</t>
+          <t>2026-08-04 21:12:12</t>
         </is>
       </c>
     </row>
@@ -708,23 +708,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>http://www.obituario.umuarama.pr.gov.br/</t>
+          <t>http://www.umuarama.pr.gov.br/secretarias/educacao</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-04 02:22:08</t>
+          <t>2026-08-04 21:12:19</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://umuarama.pr.gov.br/noticias/assistencia-social/www.flickr.com/photos/167581318@N03/albums/72177720334168307/</t>
+          <t>https://www.umuarama.pr.gov.br/noticias/assistencia-social/www.flickr.com/photos/167581318@N03/albums/72177720334168307/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,11 +748,11 @@
         <v>404</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-04 02:23:50</t>
+          <t>2026-08-04 21:18:23</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://umuarama.pr.gov.br/noticias/assistencia-social/www.flickr.com/photos/167581318@N03/albums/72177720334168307/</t>
+          <t>https://www.umuarama.pr.gov.br/noticias/assistencia-social/www.flickr.com/photos/167581318@N03/albums/72177720334168307/</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -776,11 +776,11 @@
         <v>404</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-04 02:24:03</t>
+          <t>2026-08-04 21:18:30</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-04 02:25:34</t>
+          <t>2026-08-04 21:20:57</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-04 02:25:41</t>
+          <t>2026-08-04 21:21:03</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-04 02:25:42</t>
+          <t>2026-08-04 21:21:05</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-04 02:25:54</t>
+          <t>2026-08-04 21:21:12</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-04 02:25:56</t>
+          <t>2026-08-04 21:21:14</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-04 02:26:19</t>
+          <t>2026-08-04 21:21:21</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-04 02:26:22</t>
+          <t>2026-08-04 21:21:23</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://umuarama.pr.gov.br/secretaria/meio-ambiente</t>
+          <t>https://umuarama.pr.gov.br/download_mp3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,11 +1000,11 @@
         <v>500</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-04 02:26:57</t>
+          <t>2026-08-04 21:21:29</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-04 02:27:11</t>
+          <t>2026-08-04 21:21:31</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://umuarama.pr.gov.br/public/download_mp3</t>
+          <t>https://umuarama.pr.gov.br/secretaria/meio-ambiente</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-04 02:27:13</t>
+          <t>2026-08-04 21:21:37</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>http://www.obituario.umuarama.pr.gov.br/</t>
+          <t>https://umuarama.pr.gov.br/public/download_mp3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-04 02:27:59</t>
+          <t>2026-08-04 21:21:39</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,79 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>https://umuarama.pr.gov.br/public/download_mp3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>500</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-04 21:21:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>umuarama</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>http://www.obituario.umuarama.pr.gov.br/</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-04 21:21:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>umuarama</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>http://www.obituario.umuarama.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-04 02:28:00</t>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-04 21:22:00</t>
         </is>
       </c>
     </row>
